--- a/Clarifications/Callback_analysis_clarification_CAR_data_31OCT.xlsx
+++ b/Clarifications/Callback_analysis_clarification_CAR_data_31OCT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\akl0407\Desktop\Academia\GitHub\STAT390_LegalAid_Fall2025\Clarifications\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B734DCA3-F853-4F13-8258-F9AD5E1809AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F9C327D-6AC0-465B-AA57-F5F019D7C11B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" tabRatio="679" firstSheet="1" activeTab="1" xr2:uid="{607C3898-A061-43F2-B8EC-A6C01FB58344}"/>
   </bookViews>
@@ -521,18 +521,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -552,6 +540,18 @@
     </xf>
     <xf numFmtId="22" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -584,8 +584,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>53340</xdr:colOff>
       <xdr:row>14</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
@@ -1257,121 +1257,122 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="12.68359375" customWidth="1"/>
+    <col min="4" max="5" width="12.89453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
+      <c r="L2" s="14"/>
+      <c r="M2" s="14"/>
+      <c r="N2" s="14"/>
+      <c r="O2" s="14"/>
+      <c r="P2" s="14"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="5"/>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="7"/>
-      <c r="M3" s="7"/>
-      <c r="N3" s="7"/>
-      <c r="O3" s="7"/>
-      <c r="P3" s="7"/>
+      <c r="A3" s="12"/>
+      <c r="B3" s="14"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="14"/>
+      <c r="K3" s="14"/>
+      <c r="L3" s="14"/>
+      <c r="M3" s="14"/>
+      <c r="N3" s="14"/>
+      <c r="O3" s="14"/>
+      <c r="P3" s="14"/>
     </row>
     <row r="4" spans="1:16" ht="134.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="8"/>
-      <c r="K4" s="8"/>
-      <c r="L4" s="8"/>
-      <c r="M4" s="8"/>
-      <c r="N4" s="8"/>
-      <c r="O4" s="8"/>
-      <c r="P4" s="8"/>
+      <c r="B4" s="15"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="15"/>
+      <c r="H4" s="15"/>
+      <c r="I4" s="15"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="15"/>
+      <c r="L4" s="15"/>
+      <c r="M4" s="15"/>
+      <c r="N4" s="15"/>
+      <c r="O4" s="15"/>
+      <c r="P4" s="15"/>
     </row>
     <row r="5" spans="1:16" ht="81.3" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9"/>
-      <c r="K5" s="9"/>
-      <c r="L5" s="9"/>
-      <c r="M5" s="9"/>
-      <c r="N5" s="9"/>
-      <c r="O5" s="9"/>
-      <c r="P5" s="9"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="5"/>
+      <c r="N5" s="5"/>
+      <c r="O5" s="5"/>
+      <c r="P5" s="5"/>
     </row>
     <row r="6" spans="1:16" ht="67.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="5"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7"/>
-      <c r="N6" s="7"/>
-      <c r="O6" s="7"/>
-      <c r="P6" s="7"/>
+      <c r="A6" s="12"/>
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="14"/>
+      <c r="K6" s="14"/>
+      <c r="L6" s="14"/>
+      <c r="M6" s="14"/>
+      <c r="N6" s="14"/>
+      <c r="O6" s="14"/>
+      <c r="P6" s="14"/>
     </row>
     <row r="7" spans="1:16" ht="63.3" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="5"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
-      <c r="N7" s="7"/>
-      <c r="O7" s="7"/>
-      <c r="P7" s="7"/>
+      <c r="A7" s="12"/>
+      <c r="B7" s="14"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="14"/>
+      <c r="H7" s="14"/>
+      <c r="I7" s="14"/>
+      <c r="J7" s="14"/>
+      <c r="K7" s="14"/>
+      <c r="L7" s="14"/>
+      <c r="M7" s="14"/>
+      <c r="N7" s="14"/>
+      <c r="O7" s="14"/>
+      <c r="P7" s="14"/>
     </row>
     <row r="8" spans="1:16" ht="15.3" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="4"/>
@@ -1419,40 +1420,40 @@
       <c r="A12" s="1"/>
     </row>
     <row r="13" spans="1:16" ht="67.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="5"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
-      <c r="K13" s="5"/>
-      <c r="L13" s="5"/>
-      <c r="M13" s="5"/>
-      <c r="N13" s="5"/>
-      <c r="O13" s="5"/>
-      <c r="P13" s="5"/>
+      <c r="A13" s="12"/>
+      <c r="B13" s="12"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="12"/>
+      <c r="I13" s="12"/>
+      <c r="J13" s="12"/>
+      <c r="K13" s="12"/>
+      <c r="L13" s="12"/>
+      <c r="M13" s="12"/>
+      <c r="N13" s="12"/>
+      <c r="O13" s="12"/>
+      <c r="P13" s="12"/>
     </row>
     <row r="14" spans="1:16" ht="136.19999999999999" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="6"/>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
-      <c r="K14" s="6"/>
-      <c r="L14" s="6"/>
-      <c r="M14" s="6"/>
-      <c r="N14" s="6"/>
-      <c r="O14" s="6"/>
-      <c r="P14" s="6"/>
+      <c r="A14" s="13"/>
+      <c r="B14" s="13"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="13"/>
+      <c r="H14" s="13"/>
+      <c r="I14" s="13"/>
+      <c r="J14" s="13"/>
+      <c r="K14" s="13"/>
+      <c r="L14" s="13"/>
+      <c r="M14" s="13"/>
+      <c r="N14" s="13"/>
+      <c r="O14" s="13"/>
+      <c r="P14" s="13"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="1" t="s">
@@ -1495,1222 +1496,1222 @@
       </c>
     </row>
     <row r="26" spans="1:11" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A26" s="11" t="s">
+      <c r="A26" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B26" s="12" t="s">
+      <c r="B26" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="C26" s="12" t="s">
+      <c r="C26" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="D26" s="12" t="s">
+      <c r="D26" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="E26" s="12" t="s">
+      <c r="E26" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="F26" s="12" t="s">
+      <c r="F26" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="G26" s="12" t="s">
+      <c r="G26" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="H26" s="12" t="s">
+      <c r="H26" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="I26" s="12" t="s">
+      <c r="I26" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="J26" s="12" t="s">
+      <c r="J26" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="K26" s="12" t="s">
+      <c r="K26" s="8" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A27" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="B27" s="14" t="s">
+      <c r="A27" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B27" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C27" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="D27" s="15">
+      <c r="C27" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D27" s="11">
         <v>45861.333414351851</v>
       </c>
-      <c r="E27" s="15">
+      <c r="E27" s="11">
         <v>45861.333414351851</v>
       </c>
-      <c r="F27" s="14" t="s">
+      <c r="F27" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="G27" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="H27" s="14" t="s">
+      <c r="G27" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="H27" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="I27" s="14" t="s">
+      <c r="I27" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="J27" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="K27" s="14"/>
+      <c r="J27" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="K27" s="10"/>
     </row>
     <row r="28" spans="1:11" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A28" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="B28" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="C28" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="D28" s="15">
+      <c r="A28" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B28" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D28" s="11">
         <v>45861.333414351851</v>
       </c>
-      <c r="E28" s="15">
+      <c r="E28" s="11">
         <v>45861.333414351851</v>
       </c>
-      <c r="F28" s="14" t="s">
+      <c r="F28" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="G28" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="H28" s="14" t="s">
+      <c r="G28" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="H28" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="I28" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="J28" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="K28" s="14" t="s">
+      <c r="I28" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="J28" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="K28" s="10" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A29" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="B29" s="14" t="s">
+      <c r="A29" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B29" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C29" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="D29" s="15">
+      <c r="C29" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D29" s="11">
         <v>45861.333414351851</v>
       </c>
-      <c r="E29" s="15">
+      <c r="E29" s="11">
         <v>45861.333414351851</v>
       </c>
-      <c r="F29" s="14" t="s">
+      <c r="F29" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="G29" s="14" t="s">
+      <c r="G29" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="H29" s="14" t="s">
+      <c r="H29" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="I29" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="J29" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="K29" s="14" t="s">
+      <c r="I29" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="J29" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="K29" s="10" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A30" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="B30" s="14" t="s">
+      <c r="A30" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B30" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C30" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="D30" s="15">
+      <c r="C30" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D30" s="11">
         <v>45861.333414351851</v>
       </c>
-      <c r="E30" s="15">
+      <c r="E30" s="11">
         <v>45861.335925925923</v>
       </c>
-      <c r="F30" s="14" t="s">
+      <c r="F30" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="G30" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="H30" s="14" t="s">
+      <c r="G30" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="H30" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="I30" s="14" t="s">
+      <c r="I30" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="J30" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="K30" s="14"/>
+      <c r="J30" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="K30" s="10"/>
     </row>
     <row r="31" spans="1:11" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A31" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="B31" s="14" t="s">
+      <c r="A31" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B31" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C31" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="D31" s="15">
+      <c r="C31" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D31" s="11">
         <v>45861.333541666667</v>
       </c>
-      <c r="E31" s="15">
+      <c r="E31" s="11">
         <v>45861.333541666667</v>
       </c>
-      <c r="F31" s="14" t="s">
+      <c r="F31" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="G31" s="14" t="s">
+      <c r="G31" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="H31" s="14" t="s">
+      <c r="H31" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="I31" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="J31" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="K31" s="14" t="s">
+      <c r="I31" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="J31" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="K31" s="10" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A32" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="B32" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="C32" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="D32" s="15">
+      <c r="A32" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B32" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D32" s="11">
         <v>45861.333796296298</v>
       </c>
-      <c r="E32" s="15">
+      <c r="E32" s="11">
         <v>45861.333796296298</v>
       </c>
-      <c r="F32" s="14" t="s">
+      <c r="F32" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="G32" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="H32" s="14" t="s">
+      <c r="G32" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="H32" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="I32" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="J32" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="K32" s="14" t="s">
+      <c r="I32" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="J32" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="K32" s="10" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="86.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A33" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="B33" s="14" t="s">
+      <c r="A33" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B33" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C33" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="D33" s="15">
+      <c r="C33" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D33" s="11">
         <v>45861.333796296298</v>
       </c>
-      <c r="E33" s="15">
+      <c r="E33" s="11">
         <v>45861.333796296298</v>
       </c>
-      <c r="F33" s="14" t="s">
+      <c r="F33" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="G33" s="14" t="s">
+      <c r="G33" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="H33" s="14" t="s">
+      <c r="H33" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="I33" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="J33" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="K33" s="14" t="s">
+      <c r="I33" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="J33" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="K33" s="10" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="34" spans="1:11" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A34" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="B34" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="C34" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="D34" s="15">
+      <c r="A34" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B34" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="C34" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D34" s="11">
         <v>45861.333877314813</v>
       </c>
-      <c r="E34" s="15">
+      <c r="E34" s="11">
         <v>45861.333877314813</v>
       </c>
-      <c r="F34" s="14" t="s">
+      <c r="F34" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="G34" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="H34" s="14" t="s">
+      <c r="G34" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="H34" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="I34" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="J34" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="K34" s="14" t="s">
+      <c r="I34" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="J34" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="K34" s="10" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A35" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="B35" s="14" t="s">
+      <c r="A35" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B35" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C35" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="D35" s="15">
+      <c r="C35" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D35" s="11">
         <v>45861.333877314813</v>
       </c>
-      <c r="E35" s="15">
+      <c r="E35" s="11">
         <v>45861.333877314813</v>
       </c>
-      <c r="F35" s="14" t="s">
+      <c r="F35" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="G35" s="14" t="s">
+      <c r="G35" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="H35" s="14" t="s">
+      <c r="H35" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="I35" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="J35" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="K35" s="14" t="s">
+      <c r="I35" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="J35" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="K35" s="10" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="36" spans="1:11" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A36" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="B36" s="14" t="s">
+      <c r="A36" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B36" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C36" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="D36" s="15">
+      <c r="C36" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D36" s="11">
         <v>45861.334178240744</v>
       </c>
-      <c r="E36" s="15">
+      <c r="E36" s="11">
         <v>45861.334178240744</v>
       </c>
-      <c r="F36" s="14" t="s">
+      <c r="F36" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="G36" s="14" t="s">
+      <c r="G36" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="H36" s="14" t="s">
+      <c r="H36" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="I36" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="J36" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="K36" s="14" t="s">
+      <c r="I36" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="J36" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="K36" s="10" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="37" spans="1:11" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A37" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="B37" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="C37" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="D37" s="15">
+      <c r="A37" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B37" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="C37" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D37" s="11">
         <v>45861.334907407407</v>
       </c>
-      <c r="E37" s="15">
+      <c r="E37" s="11">
         <v>45861.334907407407</v>
       </c>
-      <c r="F37" s="14" t="s">
+      <c r="F37" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="G37" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="H37" s="14" t="s">
+      <c r="G37" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="H37" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="I37" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="J37" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="K37" s="14" t="s">
+      <c r="I37" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="J37" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="K37" s="10" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="38" spans="1:11" ht="72.3" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A38" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="B38" s="14" t="s">
+      <c r="A38" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B38" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="C38" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="D38" s="15">
+      <c r="C38" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D38" s="11">
         <v>45861.334907407407</v>
       </c>
-      <c r="E38" s="15">
+      <c r="E38" s="11">
         <v>45861.334907407407</v>
       </c>
-      <c r="F38" s="14" t="s">
+      <c r="F38" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="G38" s="14" t="s">
+      <c r="G38" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="H38" s="14" t="s">
+      <c r="H38" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="I38" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="J38" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="K38" s="14" t="s">
+      <c r="I38" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="J38" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="K38" s="10" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="39" spans="1:11" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A39" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="B39" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="C39" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="D39" s="15">
+      <c r="A39" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="C39" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D39" s="11">
         <v>45861.33525462963</v>
       </c>
-      <c r="E39" s="15">
+      <c r="E39" s="11">
         <v>45861.33525462963</v>
       </c>
-      <c r="F39" s="14" t="s">
+      <c r="F39" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="G39" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="H39" s="14" t="s">
+      <c r="G39" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="H39" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="I39" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="J39" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="K39" s="14" t="s">
+      <c r="I39" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="J39" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="K39" s="10" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="40" spans="1:11" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A40" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="B40" s="14" t="s">
+      <c r="A40" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B40" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C40" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="D40" s="15">
+      <c r="C40" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D40" s="11">
         <v>45861.33525462963</v>
       </c>
-      <c r="E40" s="15">
+      <c r="E40" s="11">
         <v>45861.33525462963</v>
       </c>
-      <c r="F40" s="14" t="s">
+      <c r="F40" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="G40" s="14" t="s">
+      <c r="G40" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="H40" s="14" t="s">
+      <c r="H40" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="I40" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="J40" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="K40" s="14" t="s">
+      <c r="I40" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="J40" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="K40" s="10" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="41" spans="1:11" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A41" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="B41" s="14" t="s">
+      <c r="A41" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B41" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C41" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="D41" s="15">
+      <c r="C41" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D41" s="11">
         <v>45861.33525462963</v>
       </c>
-      <c r="E41" s="15">
+      <c r="E41" s="11">
         <v>45861.33525462963</v>
       </c>
-      <c r="F41" s="14" t="s">
+      <c r="F41" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="G41" s="14" t="s">
+      <c r="G41" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="H41" s="14" t="s">
+      <c r="H41" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="I41" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="J41" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="K41" s="14" t="s">
+      <c r="I41" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="J41" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="K41" s="10" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="42" spans="1:11" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A42" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="B42" s="14" t="s">
+      <c r="A42" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B42" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C42" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="D42" s="15">
+      <c r="C42" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D42" s="11">
         <v>45861.335914351854</v>
       </c>
-      <c r="E42" s="15">
+      <c r="E42" s="11">
         <v>45861.335914351854</v>
       </c>
-      <c r="F42" s="14" t="s">
+      <c r="F42" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="G42" s="14" t="s">
+      <c r="G42" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="H42" s="14" t="s">
+      <c r="H42" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="I42" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="J42" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="K42" s="14" t="s">
+      <c r="I42" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="J42" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="K42" s="10" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="43" spans="1:11" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A43" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="B43" s="14" t="s">
+      <c r="A43" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B43" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C43" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="D43" s="15">
+      <c r="C43" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D43" s="11">
         <v>45861.335925925923</v>
       </c>
-      <c r="E43" s="15">
+      <c r="E43" s="11">
         <v>45861.335925925923</v>
       </c>
-      <c r="F43" s="14" t="s">
+      <c r="F43" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="G43" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="H43" s="14" t="s">
+      <c r="G43" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="H43" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="I43" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="J43" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="K43" s="14"/>
+      <c r="I43" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="J43" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="K43" s="10"/>
     </row>
     <row r="44" spans="1:11" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A44" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="B44" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="C44" s="14" t="s">
+      <c r="A44" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B44" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="C44" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="D44" s="15">
+      <c r="D44" s="11">
         <v>45861.335925925923</v>
       </c>
-      <c r="E44" s="15">
+      <c r="E44" s="11">
         <v>45861.335925925923</v>
       </c>
-      <c r="F44" s="14" t="s">
+      <c r="F44" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="G44" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="H44" s="14" t="s">
+      <c r="G44" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="H44" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="I44" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="J44" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="K44" s="14"/>
+      <c r="I44" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="J44" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="K44" s="10"/>
     </row>
     <row r="45" spans="1:11" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A45" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="B45" s="14" t="s">
+      <c r="A45" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B45" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C45" s="14" t="s">
+      <c r="C45" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="D45" s="15">
+      <c r="D45" s="11">
         <v>45861.335925925923</v>
       </c>
-      <c r="E45" s="15">
+      <c r="E45" s="11">
         <v>45861.384606481479</v>
       </c>
-      <c r="F45" s="14" t="s">
+      <c r="F45" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="G45" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="H45" s="14" t="s">
+      <c r="G45" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="H45" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="I45" s="14" t="s">
+      <c r="I45" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="J45" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="K45" s="14"/>
+      <c r="J45" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="K45" s="10"/>
     </row>
     <row r="46" spans="1:11" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A46" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="B46" s="14" t="s">
+      <c r="A46" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B46" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C46" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="D46" s="15">
+      <c r="C46" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D46" s="11">
         <v>45861.335925925923</v>
       </c>
-      <c r="E46" s="15">
+      <c r="E46" s="11">
         <v>45861.335925925923</v>
       </c>
-      <c r="F46" s="14" t="s">
+      <c r="F46" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="G46" s="14" t="s">
+      <c r="G46" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="H46" s="14" t="s">
+      <c r="H46" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="I46" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="J46" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="K46" s="14" t="s">
+      <c r="I46" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="J46" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="K46" s="10" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="47" spans="1:11" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A47" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="B47" s="14" t="s">
+      <c r="A47" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B47" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C47" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="D47" s="15">
+      <c r="C47" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D47" s="11">
         <v>45861.336064814815</v>
       </c>
-      <c r="E47" s="15">
+      <c r="E47" s="11">
         <v>45861.336064814815</v>
       </c>
-      <c r="F47" s="14" t="s">
+      <c r="F47" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="G47" s="14" t="s">
+      <c r="G47" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="H47" s="14" t="s">
+      <c r="H47" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="I47" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="J47" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="K47" s="14" t="s">
+      <c r="I47" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="J47" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="K47" s="10" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="48" spans="1:11" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A48" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="B48" s="14" t="s">
+      <c r="A48" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B48" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C48" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="D48" s="15">
+      <c r="C48" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D48" s="11">
         <v>45861.339548611111</v>
       </c>
-      <c r="E48" s="15">
+      <c r="E48" s="11">
         <v>45861.339548611111</v>
       </c>
-      <c r="F48" s="14" t="s">
+      <c r="F48" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="G48" s="14" t="s">
+      <c r="G48" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="H48" s="14" t="s">
+      <c r="H48" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="I48" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="J48" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="K48" s="14" t="s">
+      <c r="I48" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="J48" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="K48" s="10" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="49" spans="1:11" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A49" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="B49" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="C49" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="D49" s="15">
+      <c r="A49" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B49" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="C49" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D49" s="11">
         <v>45861.339733796296</v>
       </c>
-      <c r="E49" s="15">
+      <c r="E49" s="11">
         <v>45861.339733796296</v>
       </c>
-      <c r="F49" s="14" t="s">
+      <c r="F49" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="G49" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="H49" s="14" t="s">
+      <c r="G49" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="H49" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="I49" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="J49" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="K49" s="14" t="s">
+      <c r="I49" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="J49" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="K49" s="10" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="50" spans="1:11" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A50" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="B50" s="14" t="s">
+      <c r="A50" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B50" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="C50" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="D50" s="15">
+      <c r="C50" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D50" s="11">
         <v>45861.339733796296</v>
       </c>
-      <c r="E50" s="15">
+      <c r="E50" s="11">
         <v>45861.339733796296</v>
       </c>
-      <c r="F50" s="14" t="s">
+      <c r="F50" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="G50" s="14" t="s">
+      <c r="G50" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="H50" s="14" t="s">
+      <c r="H50" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="I50" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="J50" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="K50" s="14" t="s">
+      <c r="I50" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="J50" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="K50" s="10" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="51" spans="1:11" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A51" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="B51" s="14" t="s">
+      <c r="A51" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B51" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="C51" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="D51" s="15">
+      <c r="C51" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D51" s="11">
         <v>45861.339861111112</v>
       </c>
-      <c r="E51" s="15">
+      <c r="E51" s="11">
         <v>45861.339861111112</v>
       </c>
-      <c r="F51" s="14" t="s">
+      <c r="F51" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="G51" s="14" t="s">
+      <c r="G51" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="H51" s="14" t="s">
+      <c r="H51" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="I51" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="J51" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="K51" s="14" t="s">
+      <c r="I51" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="J51" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="K51" s="10" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="52" spans="1:11" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A52" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="B52" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="C52" s="14" t="s">
+      <c r="A52" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B52" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="C52" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="D52" s="15">
+      <c r="D52" s="11">
         <v>45861.339861111112</v>
       </c>
-      <c r="E52" s="15">
+      <c r="E52" s="11">
         <v>45861.384606481479</v>
       </c>
-      <c r="F52" s="14" t="s">
+      <c r="F52" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="G52" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="H52" s="14" t="s">
+      <c r="G52" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="H52" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="I52" s="14" t="s">
+      <c r="I52" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="J52" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="K52" s="14" t="s">
+      <c r="J52" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="K52" s="10" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="53" spans="1:11" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A53" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="B53" s="14" t="s">
+      <c r="A53" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B53" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="C53" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="D53" s="15">
+      <c r="C53" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D53" s="11">
         <v>45861.339861111112</v>
       </c>
-      <c r="E53" s="15">
+      <c r="E53" s="11">
         <v>45861.339861111112</v>
       </c>
-      <c r="F53" s="14" t="s">
+      <c r="F53" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="G53" s="14" t="s">
+      <c r="G53" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="H53" s="14" t="s">
+      <c r="H53" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="I53" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="J53" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="K53" s="14" t="s">
+      <c r="I53" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="J53" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="K53" s="10" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="54" spans="1:11" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A54" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="B54" s="14" t="s">
+      <c r="A54" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B54" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="C54" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="D54" s="15">
+      <c r="C54" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D54" s="11">
         <v>45861.339965277781</v>
       </c>
-      <c r="E54" s="15">
+      <c r="E54" s="11">
         <v>45861.339965277781</v>
       </c>
-      <c r="F54" s="14" t="s">
+      <c r="F54" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="G54" s="14" t="s">
+      <c r="G54" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="H54" s="14" t="s">
+      <c r="H54" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="I54" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="J54" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="K54" s="14" t="s">
+      <c r="I54" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="J54" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="K54" s="10" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="55" spans="1:11" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A55" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="B55" s="14" t="s">
+      <c r="A55" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B55" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="C55" s="14" t="s">
+      <c r="C55" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="D55" s="15">
+      <c r="D55" s="11">
         <v>45861.384606481479</v>
       </c>
-      <c r="E55" s="15">
+      <c r="E55" s="11">
         <v>45861.384733796294</v>
       </c>
-      <c r="F55" s="14" t="s">
+      <c r="F55" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="G55" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="H55" s="14" t="s">
+      <c r="G55" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="H55" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="I55" s="14" t="s">
+      <c r="I55" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="J55" s="14" t="s">
+      <c r="J55" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="K55" s="14" t="s">
+      <c r="K55" s="10" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="56" spans="1:11" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A56" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="B56" s="14" t="s">
+      <c r="A56" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B56" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="C56" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="D56" s="15">
+      <c r="C56" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D56" s="11">
         <v>45861.384606481479</v>
       </c>
-      <c r="E56" s="15">
+      <c r="E56" s="11">
         <v>45861.384606481479</v>
       </c>
-      <c r="F56" s="14" t="s">
+      <c r="F56" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="G56" s="14" t="s">
+      <c r="G56" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="H56" s="14" t="s">
+      <c r="H56" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="I56" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="J56" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="K56" s="14" t="s">
+      <c r="I56" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="J56" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="K56" s="10" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="57" spans="1:11" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A57" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="B57" s="14" t="s">
+      <c r="A57" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B57" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="C57" s="14" t="s">
+      <c r="C57" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="D57" s="15">
+      <c r="D57" s="11">
         <v>45861.384733796294</v>
       </c>
-      <c r="E57" s="15">
+      <c r="E57" s="11">
         <v>45861.390034722222</v>
       </c>
-      <c r="F57" s="14" t="s">
+      <c r="F57" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="G57" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="H57" s="14" t="s">
+      <c r="G57" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="H57" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="I57" s="14" t="s">
+      <c r="I57" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="J57" s="14" t="s">
+      <c r="J57" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="K57" s="14" t="s">
+      <c r="K57" s="10" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="58" spans="1:11" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A58" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="B58" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="C58" s="14" t="s">
+      <c r="A58" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B58" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="C58" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="D58" s="15">
+      <c r="D58" s="11">
         <v>45861.390034722222</v>
       </c>
-      <c r="E58" s="15">
+      <c r="E58" s="11">
         <v>45861.391423611109</v>
       </c>
-      <c r="F58" s="14" t="s">
+      <c r="F58" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="G58" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="H58" s="14" t="s">
+      <c r="G58" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="H58" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="I58" s="14" t="s">
+      <c r="I58" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="J58" s="14" t="s">
+      <c r="J58" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="K58" s="14" t="s">
+      <c r="K58" s="10" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="59" spans="1:11" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A59" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="B59" s="14" t="s">
+      <c r="A59" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B59" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="C59" s="14" t="s">
+      <c r="C59" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="D59" s="15">
+      <c r="D59" s="11">
         <v>45861.390034722222</v>
       </c>
-      <c r="E59" s="15">
+      <c r="E59" s="11">
         <v>45861.390034722222</v>
       </c>
-      <c r="F59" s="14" t="s">
+      <c r="F59" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="G59" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="H59" s="14" t="s">
+      <c r="G59" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="H59" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="I59" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="J59" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="K59" s="14" t="s">
+      <c r="I59" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="J59" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="K59" s="10" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="60" spans="1:11" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A60" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="B60" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="C60" s="14" t="s">
+      <c r="A60" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B60" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="C60" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="D60" s="15">
+      <c r="D60" s="11">
         <v>45861.391423611109</v>
       </c>
-      <c r="E60" s="15">
+      <c r="E60" s="11">
         <v>45861.391423611109</v>
       </c>
-      <c r="F60" s="14" t="s">
+      <c r="F60" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="G60" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="H60" s="14" t="s">
+      <c r="G60" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="H60" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="I60" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="J60" s="14" t="s">
+      <c r="I60" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="J60" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="K60" s="14" t="s">
+      <c r="K60" s="10" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.55000000000000004">
-      <c r="A61" s="10"/>
+      <c r="A61" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -2733,24 +2734,24 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
     <row r="2" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
+      <c r="L2" s="14"/>
+      <c r="M2" s="14"/>
+      <c r="N2" s="14"/>
+      <c r="O2" s="14"/>
+      <c r="P2" s="14"/>
     </row>
     <row r="3" spans="1:16" ht="78.3" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="16" t="s">
